--- a/data/xlsx/bwcci--digital-marketing-freelancing-and-entrepreneurship-development.xlsx
+++ b/data/xlsx/bwcci--digital-marketing-freelancing-and-entrepreneurship-development.xlsx
@@ -99,7 +99,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
@@ -132,6 +132,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -637,7 +643,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="14" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -648,7 +654,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>8</v>
       </c>
@@ -659,7 +667,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="14" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -670,7 +678,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>6</v>
       </c>
@@ -681,7 +691,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="14" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -692,7 +702,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>6</v>
       </c>
@@ -703,7 +715,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="14" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -714,7 +726,9 @@
       <c r="C19" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>10</v>
       </c>
@@ -725,7 +739,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="14" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -736,7 +750,9 @@
       <c r="C20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>6</v>
       </c>
@@ -747,7 +763,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="14" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -758,7 +774,9 @@
       <c r="C21" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>8</v>
       </c>
@@ -769,7 +787,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="14" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -780,7 +798,9 @@
       <c r="C22" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>5</v>
       </c>
@@ -791,7 +811,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="14" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -802,7 +822,9 @@
       <c r="C23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>8</v>
       </c>
@@ -813,7 +835,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="inlineStr">
+      <c r="A24" s="15" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -821,18 +843,18 @@
       <c r="B24" s="11" t="n"/>
       <c r="C24" s="11" t="n"/>
       <c r="D24" s="12" t="n"/>
-      <c r="E24" s="10">
+      <c r="E24" s="15">
         <f>SUM(E16:E23)</f>
         <v/>
       </c>
-      <c r="F24" s="10">
+      <c r="F24" s="15">
         <f>SUM(F16:F23)</f>
         <v/>
       </c>
       <c r="G24" s="13" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="inlineStr">
+      <c r="A25" s="15" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -841,7 +863,7 @@
       <c r="C25" s="11" t="n"/>
       <c r="D25" s="11" t="n"/>
       <c r="E25" s="12" t="n"/>
-      <c r="F25" s="10">
+      <c r="F25" s="15">
         <f>F24/E24*100</f>
         <v/>
       </c>
@@ -849,7 +871,7 @@
     </row>
     <row r="26" ht="9.75" customHeight="1"/>
     <row r="27">
-      <c r="A27" s="10" t="inlineStr">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -858,11 +880,11 @@
       <c r="C27" s="11" t="n"/>
       <c r="D27" s="11" t="n"/>
       <c r="E27" s="12" t="n"/>
-      <c r="F27" s="10">
+      <c r="F27" s="15">
         <f>F25*30/100</f>
         <v/>
       </c>
-      <c r="G27" s="10" t="inlineStr">
+      <c r="G27" s="15" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
